--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>VAERS Immunizationpvac2</t>
+    <t>VAERS Immunization[pvac2]</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,10 +514,16 @@
     <t>Will generally be set to show that the immunization has been completed or not done.  This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>completed</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+  </si>
+  <si>
+    <t>2026: fixed value = #completed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,6 +557,9 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
+    <t>2027: target not supported</t>
+  </si>
+  <si>
     <t>Event.statusReason</t>
   </si>
   <si>
@@ -691,7 +700,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSPatient)
 </t>
   </si>
   <si>
@@ -699,6 +708,9 @@
   </si>
   <si>
     <t>The patient who either received or did not receive the immunization.</t>
+  </si>
+  <si>
+    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -815,6 +827,9 @@
   </si>
   <si>
     <t>Reflects the “reliability” of the content.</t>
+  </si>
+  <si>
+    <t>2028: fixed value = false</t>
   </si>
   <si>
     <t>RXA-9</t>
@@ -1858,7 +1873,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="58.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3299,7 +3314,7 @@
         <v>80</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>80</v>
@@ -3314,11 +3329,11 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3351,22 +3366,22 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3374,10 +3389,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3400,16 +3415,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3435,11 +3450,11 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3457,7 +3472,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3472,19 +3487,19 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3495,10 +3510,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3521,13 +3536,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3554,11 +3569,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3576,7 +3591,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3585,7 +3600,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3597,27 +3612,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3640,13 +3655,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3697,7 +3712,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3724,7 +3739,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3735,10 +3750,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3767,7 +3782,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3808,19 +3823,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3847,7 +3862,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3858,10 +3873,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3884,19 +3899,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3945,7 +3960,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3969,10 +3984,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3983,10 +3998,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4009,19 +4024,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4070,7 +4085,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4085,7 +4100,7 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -4094,10 +4109,10 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4108,14 +4123,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4134,13 +4149,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4191,7 +4206,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4206,22 +4221,22 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>80</v>
@@ -4229,10 +4244,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4255,13 +4270,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4312,7 +4327,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4333,16 +4348,16 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>80</v>
@@ -4350,10 +4365,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4376,16 +4391,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4423,17 +4438,17 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4454,30 +4469,30 @@
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
@@ -4499,16 +4514,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4558,7 +4573,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>91</v>
@@ -4573,33 +4588,33 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4622,13 +4637,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4679,7 +4694,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4706,10 +4721,10 @@
         <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>80</v>
@@ -4717,10 +4732,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4743,16 +4758,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4763,7 +4778,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -4802,7 +4817,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4817,7 +4832,7 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -4826,13 +4841,13 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>80</v>
@@ -4840,10 +4855,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4866,16 +4881,16 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4901,31 +4916,31 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Z25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4949,13 +4964,13 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>80</v>
@@ -4963,10 +4978,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4989,13 +5004,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5046,7 +5061,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5067,16 +5082,16 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5084,10 +5099,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5110,13 +5125,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5167,7 +5182,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5191,24 +5206,24 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5231,13 +5246,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5288,7 +5303,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5315,7 +5330,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5326,10 +5341,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5358,7 +5373,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5399,19 +5414,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5438,7 +5453,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5449,10 +5464,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5475,16 +5490,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5534,7 +5549,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5543,7 +5558,7 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
@@ -5572,10 +5587,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5601,13 +5616,13 @@
         <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5633,13 +5648,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5657,7 +5672,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5695,10 +5710,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5724,13 +5739,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5780,7 +5795,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5807,7 +5822,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5818,10 +5833,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5844,16 +5859,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5903,7 +5918,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5918,7 +5933,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5941,10 +5956,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5967,13 +5982,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6024,7 +6039,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6039,7 +6054,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -6048,24 +6063,24 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6088,13 +6103,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6145,7 +6160,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6169,10 +6184,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6183,10 +6198,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6209,13 +6224,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6242,13 +6257,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6266,7 +6281,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6281,7 +6296,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -6290,24 +6305,24 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6330,13 +6345,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6363,13 +6378,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6387,7 +6402,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6402,7 +6417,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>80</v>
@@ -6411,24 +6426,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6451,13 +6466,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6508,7 +6523,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6532,10 +6547,10 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6546,10 +6561,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6572,13 +6587,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6629,7 +6644,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6650,13 +6665,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6667,10 +6682,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6693,13 +6708,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6750,7 +6765,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6777,7 +6792,7 @@
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6803,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6820,7 +6835,7 @@
         <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -6873,7 +6888,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6900,7 +6915,7 @@
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6911,14 +6926,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6940,10 +6955,10 @@
         <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>140</v>
@@ -6998,7 +7013,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7036,10 +7051,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7062,13 +7077,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7095,13 +7110,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -7119,7 +7134,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7140,13 +7155,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7157,10 +7172,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7183,16 +7198,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7242,7 +7257,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>91</v>
@@ -7263,16 +7278,16 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -7280,10 +7295,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7306,13 +7321,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7363,7 +7378,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7384,13 +7399,13 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7401,10 +7416,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7427,13 +7442,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7460,13 +7475,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7484,7 +7499,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7505,13 +7520,13 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7522,10 +7537,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7548,13 +7563,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7605,7 +7620,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7626,7 +7641,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7643,10 +7658,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7669,23 +7684,23 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="R48" t="s" s="2">
         <v>80</v>
@@ -7730,7 +7745,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7754,7 +7769,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>134</v>
@@ -7768,10 +7783,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7794,13 +7809,13 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7827,13 +7842,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7851,7 +7866,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7889,10 +7904,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7915,13 +7930,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7972,7 +7987,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7984,7 +7999,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -8010,10 +8025,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8036,13 +8051,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8093,7 +8108,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8120,7 +8135,7 @@
         <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8146,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8163,7 +8178,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -8216,7 +8231,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8243,7 +8258,7 @@
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8254,14 +8269,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8283,10 +8298,10 @@
         <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>140</v>
@@ -8341,7 +8356,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8379,10 +8394,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8405,13 +8420,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8462,7 +8477,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8486,7 +8501,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>134</v>
@@ -8500,10 +8515,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8529,10 +8544,10 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8583,7 +8598,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8621,10 +8636,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8647,13 +8662,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8704,7 +8719,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8728,7 +8743,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>134</v>
@@ -8742,10 +8757,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8768,13 +8783,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8825,7 +8840,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8849,7 +8864,7 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>134</v>
@@ -8863,10 +8878,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8889,13 +8904,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8922,13 +8937,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8946,7 +8961,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8970,7 +8985,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -8984,10 +8999,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9010,13 +9025,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9043,13 +9058,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9067,7 +9082,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9105,10 +9120,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9131,16 +9146,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9190,7 +9205,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9214,10 +9229,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9228,10 +9243,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9254,13 +9269,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9311,7 +9326,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9338,7 +9353,7 @@
         <v>80</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9349,10 +9364,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9381,7 +9396,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -9434,7 +9449,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9461,7 +9476,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9472,14 +9487,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9501,10 +9516,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -9559,7 +9574,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9597,10 +9612,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9623,13 +9638,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9680,7 +9695,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9704,10 +9719,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9718,10 +9733,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9744,13 +9759,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9801,7 +9816,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9825,10 +9840,10 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9839,10 +9854,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9865,13 +9880,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9922,7 +9937,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9946,10 +9961,10 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9960,10 +9975,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9986,13 +10001,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10043,7 +10058,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10081,10 +10096,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10107,13 +10122,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10164,7 +10179,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10191,7 +10206,7 @@
         <v>80</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10202,10 +10217,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10234,7 +10249,7 @@
         <v>138</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -10287,7 +10302,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10314,7 +10329,7 @@
         <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10325,14 +10340,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10354,10 +10369,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10412,7 +10427,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10450,10 +10465,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10476,13 +10491,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10533,7 +10548,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10571,10 +10586,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10597,13 +10612,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10654,7 +10669,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10692,10 +10707,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10718,13 +10733,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10751,13 +10766,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10775,7 +10790,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10813,10 +10828,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10839,16 +10854,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10886,17 +10901,17 @@
         <v>80</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>91</v>
@@ -10934,13 +10949,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="B75" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="C75" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>80</v>
@@ -10962,16 +10977,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11021,7 +11036,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>91</v>
@@ -11036,7 +11051,7 @@
         <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
@@ -11059,10 +11074,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11085,16 +11100,16 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11144,7 +11159,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1927: source value from ADERS - 22_PVac2_TypeBrand</t>
+    <t>1927: source value based on ADERS - 22_PVac2_TypeBrand</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -707,7 +707,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference based on ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -792,7 +792,7 @@
 </t>
   </si>
   <si>
-    <t>1933: source value from ADERS - 22_PVac2_Date</t>
+    <t>1933: source value based on ADERS - 22_PVac2_Date</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -989,7 +989,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1928: source value from ADERS - 22_PVac2_Mfgr</t>
+    <t>1928: source value based on ADERS - 22_PVac2_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -1001,7 +1001,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1929: source value from ADERS - 22_PVac2_Lot</t>
+    <t>1929: source value based on ADERS - 22_PVac2_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1047,7 +1047,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1931: source value from ADERS - 22_PVac2_Site</t>
+    <t>1931: source value based on ADERS - 22_PVac2_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1074,7 +1074,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1930: source value from ADERS - 22_PVac2_Route</t>
+    <t>1930: source value based on ADERS - 22_PVac2_Route</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1531,7 +1531,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1932: source value from ADERS - 22_PVac2_DoseInSeries</t>
+    <t>1932: source value based on ADERS - 22_PVac2_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1927: source value based on ADERS - 22_PVac2_TypeBrand</t>
+    <t>1927: source value based on ADERS - 22_PVac2_TypeBrand (22-2.1)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -707,7 +707,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference based on ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference based on ADERS - 0_Pt_ICN_Full (0)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -792,7 +792,7 @@
 </t>
   </si>
   <si>
-    <t>1933: source value based on ADERS - 22_PVac2_Date</t>
+    <t>1933: source value based on ADERS - 22_PVac2_Date (22-2.7)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -989,7 +989,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1928: source value based on ADERS - 22_PVac2_Mfgr</t>
+    <t>1928: source value based on ADERS - 22_PVac2_Mfgr (22-2.2)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -1001,7 +1001,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1929: source value based on ADERS - 22_PVac2_Lot</t>
+    <t>1929: source value based on ADERS - 22_PVac2_Lot (22-2.3)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1047,7 +1047,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1931: source value based on ADERS - 22_PVac2_Site</t>
+    <t>1931: source value based on ADERS - 22_PVac2_Site (22-2.5)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1074,7 +1074,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1930: source value based on ADERS - 22_PVac2_Route</t>
+    <t>1930: source value based on ADERS - 22_PVac2_Route (22-2.4)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1531,7 +1531,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1932: source value based on ADERS - 22_PVac2_DoseInSeries</t>
+    <t>1932: source value based on ADERS - 22_PVac2_DoseInSeries (22-2.6)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationpvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
